--- a/artfynd/A 31781-2023 artfynd.xlsx
+++ b/artfynd/A 31781-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31781-2023 artfynd.xlsx
+++ b/artfynd/A 31781-2023 artfynd.xlsx
@@ -675,68 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57714329</v>
+        <v>69527599</v>
       </c>
       <c r="B2" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101479</v>
+        <v>1114</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567118.2096773953</v>
+        <v>567200</v>
       </c>
       <c r="R2" t="n">
-        <v>6261104.150826975</v>
+        <v>6261111</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,24 +743,14 @@
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karl Nordström</t>
+          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Helén Wåhlstrand Persson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,11 +762,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bryn</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>skogsek</t>
@@ -807,30 +772,20 @@
           <t>Quercus robur</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Omkrets 293</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Levande (4a) # Quercus robur # Omkrets 293</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>135909</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Jonas Hedin</t>
+          <t>Via Thomas Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -841,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69527599</v>
+        <v>102976427</v>
       </c>
       <c r="B3" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,14 +827,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalmar län (lokalnamn saknas), Sm</t>
+          <t>Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567199.9833563211</v>
+        <v>567199</v>
       </c>
       <c r="R3" t="n">
-        <v>6261110.970106175</v>
+        <v>6261111</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,53 +859,48 @@
           <t>Halltorp</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>A54DB57C-E760-4EF4-B15F-1D1FE6562FF2</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Kalmar läns trädinventering, Observatör Helén Wåhlstrand Persson</t>
+          <t>Påträffad i samband med trädinventering.</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -966,12 +911,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Thomas Johansson</t>
+          <t>Helén Wåhlstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Trädinventeringen i Kalmar län</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
@@ -980,12 +925,7 @@
         <v>69527600</v>
       </c>
       <c r="B4" t="n">
-        <v>73593</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567199.9833563211</v>
+        <v>567200</v>
       </c>
       <c r="R4" t="n">
-        <v>6261110.970106175</v>
+        <v>6261111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1050,19 +990,9 @@
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2009-03-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1116,12 +1046,7 @@
         <v>102976354</v>
       </c>
       <c r="B5" t="n">
-        <v>73593</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567198.8858906158</v>
+        <v>567199</v>
       </c>
       <c r="R5" t="n">
-        <v>6261110.400552865</v>
+        <v>6261111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1191,19 +1116,9 @@
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2009-03-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1243,7 +1158,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helén Wåhlstrand Persson</t>
+          <t>Helén Wåhlstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1254,53 +1169,63 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102976427</v>
+        <v>57714329</v>
       </c>
       <c r="B6" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1114</v>
+        <v>101479</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalmar län, Sm</t>
+          <t>Kalmar län (lokalnamn saknas), Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567198.8858906158</v>
+        <v>567118</v>
       </c>
       <c r="R6" t="n">
-        <v>6261110.400552865</v>
+        <v>6261104</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1322,74 +1247,74 @@
           <t>Halltorp</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>A54DB57C-E760-4EF4-B15F-1D1FE6562FF2</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2009-03-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad i samband med trädinventering.</t>
+          <t>Länsstyrelsen i Kalmars trädinventering, Observatör Karl Nordström</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Bryn</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Omkrets 293</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Levande (4a) # Quercus robur # Omkrets 293</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>135909</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helén Wåhlstrand Persson</t>
+          <t>Via Jonas Hedin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 31781-2023 artfynd.xlsx
+++ b/artfynd/A 31781-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527599</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102976427</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527600</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102976354</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,8 +1342,20 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714329</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>